--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486317_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486317_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.3249</v>
+        <v>9.3414</v>
       </c>
       <c r="E2" t="n">
-        <v>7.5144</v>
+        <v>8.253399999999999</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8105</v>
+        <v>1.0879</v>
       </c>
       <c r="G2" t="n">
         <v>7.6162</v>
@@ -610,13 +610,13 @@
         <v>1.9576</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.008500000000000001</v>
+        <v>1.0079</v>
       </c>
       <c r="T2" t="n">
-        <v>0.0036</v>
+        <v>0.7427</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.0121</v>
+        <v>0.2653</v>
       </c>
       <c r="V2" t="n">
         <v>0.9347</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>C. OKANU</t>
+          <t>S. MC DONNELL</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.7212</v>
+        <v>4.1729</v>
       </c>
       <c r="E3" t="n">
-        <v>2.409</v>
+        <v>2.5754</v>
       </c>
       <c r="F3" t="n">
-        <v>1.3122</v>
+        <v>1.5975</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.6425</v>
+        <v>2.9335</v>
       </c>
       <c r="H3" t="n">
-        <v>-1.3533</v>
+        <v>-0.4045</v>
       </c>
       <c r="I3" t="n">
-        <v>0.7108</v>
+        <v>3.338</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.4081</v>
+        <v>2.7592</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.5229</v>
+        <v>0.4443</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1147</v>
+        <v>2.3149</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.2344</v>
+        <v>0.1743</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.8304</v>
+        <v>-0.8488</v>
       </c>
       <c r="O3" t="n">
-        <v>0.596</v>
+        <v>1.0231</v>
       </c>
       <c r="P3" t="n">
-        <v>1.5225</v>
+        <v>0.87</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-1.0875</v>
       </c>
       <c r="R3" t="n">
-        <v>1.5225</v>
+        <v>1.9576</v>
       </c>
       <c r="S3" t="n">
-        <v>2.4714</v>
+        <v>0.9343</v>
       </c>
       <c r="T3" t="n">
-        <v>1.6872</v>
+        <v>0.9036999999999999</v>
       </c>
       <c r="U3" t="n">
-        <v>0.7842</v>
+        <v>0.0306</v>
       </c>
       <c r="V3" t="n">
-        <v>0.3698</v>
+        <v>-0.5649999999999999</v>
       </c>
       <c r="W3" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.7602</v>
+        <v>-0.5649999999999999</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>S. MC DONNELL</t>
+          <t>M. IGLESIAS FERNANDEZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.5727</v>
+        <v>3.1271</v>
       </c>
       <c r="E4" t="n">
-        <v>2.2834</v>
+        <v>2.1334</v>
       </c>
       <c r="F4" t="n">
-        <v>1.2893</v>
+        <v>0.9937</v>
       </c>
       <c r="G4" t="n">
-        <v>2.9335</v>
+        <v>1.3982</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.4045</v>
+        <v>1.9616</v>
       </c>
       <c r="I4" t="n">
-        <v>3.338</v>
+        <v>-0.5634</v>
       </c>
       <c r="J4" t="n">
-        <v>2.7592</v>
+        <v>2.2214</v>
       </c>
       <c r="K4" t="n">
-        <v>0.4443</v>
+        <v>1.5329</v>
       </c>
       <c r="L4" t="n">
-        <v>2.3149</v>
+        <v>0.6885</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1743</v>
+        <v>-0.8233</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.8488</v>
+        <v>0.4286</v>
       </c>
       <c r="O4" t="n">
-        <v>1.0231</v>
+        <v>-1.2519</v>
       </c>
       <c r="P4" t="n">
-        <v>0.87</v>
+        <v>1.0875</v>
       </c>
       <c r="Q4" t="n">
         <v>-1.0875</v>
       </c>
       <c r="R4" t="n">
-        <v>1.9576</v>
+        <v>2.1751</v>
       </c>
       <c r="S4" t="n">
-        <v>0.3341</v>
+        <v>-0.6838</v>
       </c>
       <c r="T4" t="n">
-        <v>0.6117</v>
+        <v>-0.3256</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.2776</v>
+        <v>-0.3581</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.5649999999999999</v>
+        <v>1.3252</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.3252</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.5649999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M. IGLESIAS FERNANDEZ</t>
+          <t>S. HUGUET CARRASCO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.3622</v>
+        <v>3.1158</v>
       </c>
       <c r="E5" t="n">
-        <v>2.2452</v>
+        <v>0.2029</v>
       </c>
       <c r="F5" t="n">
-        <v>1.117</v>
+        <v>2.9129</v>
       </c>
       <c r="G5" t="n">
-        <v>1.3982</v>
+        <v>2.2918</v>
       </c>
       <c r="H5" t="n">
-        <v>1.9616</v>
+        <v>1.9555</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.5634</v>
+        <v>0.3363</v>
       </c>
       <c r="J5" t="n">
-        <v>2.2214</v>
+        <v>0.5706</v>
       </c>
       <c r="K5" t="n">
-        <v>1.5329</v>
+        <v>1.2775</v>
       </c>
       <c r="L5" t="n">
-        <v>0.6885</v>
+        <v>-0.7068</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.8233</v>
+        <v>1.7212</v>
       </c>
       <c r="N5" t="n">
-        <v>0.4286</v>
+        <v>0.6781</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.2519</v>
+        <v>1.0431</v>
       </c>
       <c r="P5" t="n">
         <v>1.0875</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.0875</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>2.1751</v>
+        <v>1.0875</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.4487</v>
+        <v>-0.6333</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.2139</v>
+        <v>-0.3677</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.2348</v>
+        <v>-0.2656</v>
       </c>
       <c r="V5" t="n">
-        <v>1.3252</v>
+        <v>0.3698</v>
       </c>
       <c r="W5" t="n">
-        <v>1.3252</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>0.3698</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.8656</v>
+        <v>2.6151</v>
       </c>
       <c r="E6" t="n">
-        <v>1.7849</v>
+        <v>1.2261</v>
       </c>
       <c r="F6" t="n">
-        <v>1.0807</v>
+        <v>1.389</v>
       </c>
       <c r="G6" t="n">
         <v>1.7383</v>
@@ -922,13 +922,13 @@
         <v>1.7401</v>
       </c>
       <c r="S6" t="n">
-        <v>0.3221</v>
+        <v>0.07149999999999999</v>
       </c>
       <c r="T6" t="n">
-        <v>0.9542</v>
+        <v>0.3954</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.6321</v>
+        <v>-0.3239</v>
       </c>
       <c r="V6" t="n">
         <v>-0.9347</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>S. HUGUET CARRASCO</t>
+          <t>C. OKANU</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>2.7575</v>
+        <v>2.1721</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0912</v>
+        <v>1.2914</v>
       </c>
       <c r="F7" t="n">
-        <v>2.6663</v>
+        <v>0.8807</v>
       </c>
       <c r="G7" t="n">
-        <v>2.2918</v>
+        <v>-0.6425</v>
       </c>
       <c r="H7" t="n">
-        <v>1.9555</v>
+        <v>-1.3533</v>
       </c>
       <c r="I7" t="n">
-        <v>0.3363</v>
+        <v>0.7108</v>
       </c>
       <c r="J7" t="n">
-        <v>0.5706</v>
+        <v>-0.4081</v>
       </c>
       <c r="K7" t="n">
-        <v>1.2775</v>
+        <v>-0.5229</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.7068</v>
+        <v>0.1147</v>
       </c>
       <c r="M7" t="n">
-        <v>1.7212</v>
+        <v>-0.2344</v>
       </c>
       <c r="N7" t="n">
-        <v>0.6781</v>
+        <v>-0.8304</v>
       </c>
       <c r="O7" t="n">
-        <v>1.0431</v>
+        <v>0.596</v>
       </c>
       <c r="P7" t="n">
-        <v>1.0875</v>
+        <v>1.5225</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.0875</v>
+        <v>1.5225</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.9916</v>
+        <v>0.9223</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.4795</v>
+        <v>0.5696</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.5122</v>
+        <v>0.3527</v>
       </c>
       <c r="V7" t="n">
         <v>0.3698</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X7" t="n">
-        <v>0.3698</v>
+        <v>-0.7602</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>M. FERNANDEZ CARBALLO</t>
+          <t>I. VAZQUEZ PEREZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>2.1671</v>
+        <v>2.0956</v>
       </c>
       <c r="E8" t="n">
-        <v>2.2603</v>
+        <v>-0.6437</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.09320000000000001</v>
+        <v>2.7393</v>
       </c>
       <c r="G8" t="n">
-        <v>0.7027</v>
+        <v>-0.3</v>
       </c>
       <c r="H8" t="n">
-        <v>0.5051</v>
+        <v>-0.292</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1976</v>
+        <v>-0.008</v>
       </c>
       <c r="J8" t="n">
-        <v>1.075</v>
+        <v>-1.7207</v>
       </c>
       <c r="K8" t="n">
-        <v>0.922</v>
+        <v>-1.0521</v>
       </c>
       <c r="L8" t="n">
-        <v>0.153</v>
+        <v>-0.6686</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.3723</v>
+        <v>1.4207</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.4169</v>
+        <v>0.7601</v>
       </c>
       <c r="O8" t="n">
-        <v>0.0446</v>
+        <v>0.6606</v>
       </c>
       <c r="P8" t="n">
-        <v>1.305</v>
+        <v>1.7401</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.305</v>
+        <v>1.7401</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.2311</v>
+        <v>-0.8649</v>
       </c>
       <c r="T8" t="n">
-        <v>0.5997</v>
+        <v>-0.4434</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.8307</v>
+        <v>-0.4215</v>
       </c>
       <c r="V8" t="n">
-        <v>0.3904</v>
+        <v>1.5204</v>
       </c>
       <c r="W8" t="n">
-        <v>0.5857</v>
+        <v>1.5204</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.1952</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>I. VAZQUEZ PEREZ</t>
+          <t>M. FERNANDEZ CARBALLO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>2.0493</v>
+        <v>1.8241</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.0907</v>
+        <v>1.7015</v>
       </c>
       <c r="F9" t="n">
-        <v>3.14</v>
+        <v>0.1226</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.3</v>
+        <v>0.7027</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.292</v>
+        <v>0.5051</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.008</v>
+        <v>0.1976</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.7207</v>
+        <v>1.075</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.0521</v>
+        <v>0.922</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.6686</v>
+        <v>0.153</v>
       </c>
       <c r="M9" t="n">
-        <v>1.4207</v>
+        <v>-0.3723</v>
       </c>
       <c r="N9" t="n">
-        <v>0.7601</v>
+        <v>-0.4169</v>
       </c>
       <c r="O9" t="n">
-        <v>0.6606</v>
+        <v>0.0446</v>
       </c>
       <c r="P9" t="n">
-        <v>1.7401</v>
+        <v>1.305</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.7401</v>
+        <v>1.305</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.9113</v>
+        <v>-0.5741000000000001</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.8904</v>
+        <v>0.0409</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.0208</v>
+        <v>-0.615</v>
       </c>
       <c r="V9" t="n">
-        <v>1.5204</v>
+        <v>0.3904</v>
       </c>
       <c r="W9" t="n">
-        <v>1.5204</v>
+        <v>0.5857</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-0.1952</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>R. GILL</t>
+          <t>G. KALSCHEUR</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,64 +1189,64 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.6004</v>
+        <v>0.3041</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.7089</v>
+        <v>-0.3831</v>
       </c>
       <c r="F10" t="n">
-        <v>1.3093</v>
+        <v>0.6872</v>
       </c>
       <c r="G10" t="n">
-        <v>1.6398</v>
+        <v>-0.0449</v>
       </c>
       <c r="H10" t="n">
-        <v>0.3712</v>
+        <v>-1.0856</v>
       </c>
       <c r="I10" t="n">
-        <v>1.2686</v>
+        <v>1.0407</v>
       </c>
       <c r="J10" t="n">
-        <v>0.1011</v>
+        <v>0.6589</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0246</v>
+        <v>-0.3372</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0765</v>
+        <v>0.9961</v>
       </c>
       <c r="M10" t="n">
-        <v>1.5387</v>
+        <v>-0.7038</v>
       </c>
       <c r="N10" t="n">
-        <v>0.3466</v>
+        <v>-0.7484</v>
       </c>
       <c r="O10" t="n">
-        <v>1.1921</v>
+        <v>0.0446</v>
       </c>
       <c r="P10" t="n">
-        <v>-2.1751</v>
+        <v>-0</v>
       </c>
       <c r="Q10" t="n">
         <v>-2.1751</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>2.1751</v>
       </c>
       <c r="S10" t="n">
-        <v>2.4609</v>
+        <v>1.2837</v>
       </c>
       <c r="T10" t="n">
-        <v>1.3651</v>
+        <v>0.7427</v>
       </c>
       <c r="U10" t="n">
-        <v>1.0958</v>
+        <v>0.5411</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.3252</v>
+        <v>-0.9347</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>0.3904</v>
       </c>
       <c r="X10" t="n">
         <v>-1.3252</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.4279</v>
+        <v>0.1686</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.1936</v>
+        <v>-1.5663</v>
       </c>
       <c r="F11" t="n">
-        <v>1.7657</v>
+        <v>1.7349</v>
       </c>
       <c r="G11" t="n">
         <v>-2.6319</v>
@@ -1312,13 +1312,13 @@
         <v>2.8276</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.1886</v>
+        <v>-0.5921</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.4879</v>
+        <v>0.1394</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.7007</v>
+        <v>-0.7315</v>
       </c>
       <c r="V11" t="n">
         <v>0.5649999999999999</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>G. KALSCHEUR</t>
+          <t>R. GILL</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,64 +1345,64 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.6506999999999999</v>
+        <v>-0.4254</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.1221</v>
+        <v>-1.0874</v>
       </c>
       <c r="F12" t="n">
-        <v>0.4714</v>
+        <v>0.662</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.0449</v>
+        <v>1.6398</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.0856</v>
+        <v>0.3712</v>
       </c>
       <c r="I12" t="n">
-        <v>1.0407</v>
+        <v>1.2686</v>
       </c>
       <c r="J12" t="n">
-        <v>0.6589</v>
+        <v>0.1011</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.3372</v>
+        <v>0.0246</v>
       </c>
       <c r="L12" t="n">
-        <v>0.9961</v>
+        <v>0.0765</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.7038</v>
+        <v>1.5387</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.7484</v>
+        <v>0.3466</v>
       </c>
       <c r="O12" t="n">
-        <v>0.0446</v>
+        <v>1.1921</v>
       </c>
       <c r="P12" t="n">
-        <v>-0</v>
+        <v>-2.1751</v>
       </c>
       <c r="Q12" t="n">
         <v>-2.1751</v>
       </c>
       <c r="R12" t="n">
-        <v>2.1751</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>0.3289</v>
+        <v>1.4351</v>
       </c>
       <c r="T12" t="n">
-        <v>0.0036</v>
+        <v>0.9866</v>
       </c>
       <c r="U12" t="n">
-        <v>0.3253</v>
+        <v>0.4485</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.9347</v>
+        <v>-1.3252</v>
       </c>
       <c r="W12" t="n">
-        <v>0.3904</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
         <v>-1.3252</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.2165</v>
+        <v>-2.0431</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.1005</v>
+        <v>0.0113</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.1161</v>
+        <v>-2.0544</v>
       </c>
       <c r="G13" t="n">
         <v>0.4835</v>
@@ -1468,13 +1468,13 @@
         <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.2449</v>
+        <v>-0.07149999999999999</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.137</v>
+        <v>-0.0252</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.1079</v>
+        <v>-0.0463</v>
       </c>
       <c r="V13" t="n">
         <v>-2.4552</v>
@@ -1501,19 +1501,19 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>26.1258</v>
+        <v>26.4683</v>
       </c>
       <c r="E14" t="n">
-        <v>13.3726</v>
+        <v>13.7149</v>
       </c>
       <c r="F14" t="n">
-        <v>12.7531</v>
+        <v>12.7533</v>
       </c>
       <c r="G14" t="n">
         <v>15.1847</v>
       </c>
       <c r="H14" t="n">
-        <v>6.1445</v>
+        <v>6.144500000000001</v>
       </c>
       <c r="I14" t="n">
         <v>9.0402</v>
@@ -1522,22 +1522,22 @@
         <v>12.7796</v>
       </c>
       <c r="K14" t="n">
-        <v>6.4205</v>
+        <v>6.420500000000001</v>
       </c>
       <c r="L14" t="n">
-        <v>6.359100000000001</v>
+        <v>6.359100000000002</v>
       </c>
       <c r="M14" t="n">
         <v>2.4051</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.276</v>
+        <v>-0.2759999999999998</v>
       </c>
       <c r="O14" t="n">
         <v>2.6812</v>
       </c>
       <c r="P14" t="n">
-        <v>9.787700000000001</v>
+        <v>9.787699999999999</v>
       </c>
       <c r="Q14" t="n">
         <v>-8.7003</v>
@@ -1546,16 +1546,16 @@
         <v>18.4882</v>
       </c>
       <c r="S14" t="n">
-        <v>1.8927</v>
+        <v>2.235100000000001</v>
       </c>
       <c r="T14" t="n">
-        <v>3.0164</v>
+        <v>3.3591</v>
       </c>
       <c r="U14" t="n">
-        <v>-1.1236</v>
+        <v>-1.1237</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.7394999999999992</v>
+        <v>-0.7395000000000003</v>
       </c>
       <c r="W14" t="n">
         <v>6.276899999999999</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>E. IDEHEN IDEHEN</t>
+          <t>A. DOMENECH FONTANA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.867</v>
+        <v>0.7323</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.0668</v>
+        <v>1.2102</v>
       </c>
       <c r="F15" t="n">
-        <v>0.9338</v>
+        <v>-0.4779</v>
       </c>
       <c r="G15" t="n">
-        <v>0.1343</v>
+        <v>-0.2102</v>
       </c>
       <c r="H15" t="n">
-        <v>0.3375</v>
+        <v>1.6058</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.2032</v>
+        <v>-1.816</v>
       </c>
       <c r="J15" t="n">
-        <v>1.2827</v>
+        <v>0.1955</v>
       </c>
       <c r="K15" t="n">
-        <v>1.168</v>
+        <v>1.6091</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1147</v>
+        <v>-1.4136</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.1484</v>
+        <v>-0.4057</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.8304</v>
+        <v>-0.0033</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.318</v>
+        <v>-0.4024</v>
       </c>
       <c r="P15" t="n">
         <v>-0.87</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.0875</v>
+        <v>-1.305</v>
       </c>
       <c r="R15" t="n">
-        <v>0.2175</v>
+        <v>0.435</v>
       </c>
       <c r="S15" t="n">
-        <v>1.2329</v>
+        <v>-0.2728</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.262</v>
+        <v>0.2343</v>
       </c>
       <c r="U15" t="n">
-        <v>1.4949</v>
+        <v>-0.5071</v>
       </c>
       <c r="V15" t="n">
-        <v>0.3698</v>
+        <v>2.0854</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>2.0854</v>
       </c>
       <c r="X15" t="n">
-        <v>0.3698</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. HARGUINDEY MANEIRO</t>
+          <t>E. IDEHEN IDEHEN</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.2112</v>
+        <v>0.6976</v>
       </c>
       <c r="E16" t="n">
-        <v>2.6381</v>
+        <v>0.3802</v>
       </c>
       <c r="F16" t="n">
-        <v>-2.4268</v>
+        <v>0.3173</v>
       </c>
       <c r="G16" t="n">
-        <v>0.8601</v>
+        <v>0.1343</v>
       </c>
       <c r="H16" t="n">
-        <v>1.1159</v>
+        <v>0.3375</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.2558</v>
+        <v>-0.2032</v>
       </c>
       <c r="J16" t="n">
-        <v>2.5473</v>
+        <v>1.2827</v>
       </c>
       <c r="K16" t="n">
-        <v>1.5512</v>
+        <v>1.168</v>
       </c>
       <c r="L16" t="n">
-        <v>0.9961</v>
+        <v>0.1147</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.6872</v>
+        <v>-1.1484</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.4353</v>
+        <v>-0.8304</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.2519</v>
+        <v>-0.318</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>-0.87</v>
       </c>
       <c r="Q16" t="n">
         <v>-1.0875</v>
       </c>
       <c r="R16" t="n">
-        <v>1.0875</v>
+        <v>0.2175</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.2792</v>
+        <v>1.0635</v>
       </c>
       <c r="T16" t="n">
-        <v>0.0277</v>
+        <v>0.1851</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.3068</v>
+        <v>0.8784</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.3698</v>
+        <v>0.3698</v>
       </c>
       <c r="W16" t="n">
-        <v>1.1507</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.5204</v>
+        <v>0.3698</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. DOMENECH FONTANA</t>
+          <t>S. SVEJCAR</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,64 +1735,64 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0272</v>
+        <v>0.6425</v>
       </c>
       <c r="E17" t="n">
-        <v>0.8749</v>
+        <v>1.6018</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.8477</v>
+        <v>-0.9593</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.2102</v>
+        <v>0.3595</v>
       </c>
       <c r="H17" t="n">
-        <v>1.6058</v>
+        <v>-0.6206</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.816</v>
+        <v>0.9802</v>
       </c>
       <c r="J17" t="n">
-        <v>0.1955</v>
+        <v>1.834</v>
       </c>
       <c r="K17" t="n">
-        <v>1.6091</v>
+        <v>-0.1</v>
       </c>
       <c r="L17" t="n">
-        <v>-1.4136</v>
+        <v>1.934</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.4057</v>
+        <v>-1.4745</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.0033</v>
+        <v>-0.5206</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.4024</v>
+        <v>-0.9539</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.87</v>
+        <v>0.2175</v>
       </c>
       <c r="Q17" t="n">
         <v>-1.305</v>
       </c>
       <c r="R17" t="n">
-        <v>0.435</v>
+        <v>1.5225</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.9779</v>
+        <v>-1.2597</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.1009</v>
+        <v>-0.2523</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.877</v>
+        <v>-1.0073</v>
       </c>
       <c r="V17" t="n">
-        <v>2.0854</v>
+        <v>1.3252</v>
       </c>
       <c r="W17" t="n">
-        <v>2.0854</v>
+        <v>1.3252</v>
       </c>
       <c r="X17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>M. AYESA RODRIGUEZ</t>
+          <t>A. HARGUINDEY MANEIRO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.2978</v>
+        <v>-0.1048</v>
       </c>
       <c r="E18" t="n">
-        <v>0.0182</v>
+        <v>2.4146</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.3161</v>
+        <v>-2.5193</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.0152</v>
+        <v>0.8601</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.1642</v>
+        <v>1.1159</v>
       </c>
       <c r="I18" t="n">
-        <v>0.149</v>
+        <v>-0.2558</v>
       </c>
       <c r="J18" t="n">
-        <v>0.0182</v>
+        <v>2.5473</v>
       </c>
       <c r="K18" t="n">
-        <v>0.0182</v>
+        <v>1.5512</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>0.9961</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.0335</v>
+        <v>-1.6872</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.1825</v>
+        <v>-0.4353</v>
       </c>
       <c r="O18" t="n">
-        <v>0.149</v>
+        <v>-1.2519</v>
       </c>
       <c r="P18" t="n">
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-1.0875</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.0875</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.08740000000000001</v>
+        <v>-0.5951</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>-0.1959</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.08740000000000001</v>
+        <v>-0.3993</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.1952</v>
+        <v>-0.3698</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.1507</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.1952</v>
+        <v>-1.5204</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>S. SVEJCAR</t>
+          <t>M. AYESA RODRIGUEZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.5777</v>
+        <v>-0.2054</v>
       </c>
       <c r="E19" t="n">
-        <v>0.9313</v>
+        <v>0.0182</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.509</v>
+        <v>-0.2236</v>
       </c>
       <c r="G19" t="n">
-        <v>0.3595</v>
+        <v>-0.0152</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.6206</v>
+        <v>-0.1642</v>
       </c>
       <c r="I19" t="n">
-        <v>0.9802</v>
+        <v>0.149</v>
       </c>
       <c r="J19" t="n">
-        <v>1.834</v>
+        <v>0.0182</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.1</v>
+        <v>0.0182</v>
       </c>
       <c r="L19" t="n">
-        <v>1.934</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.4745</v>
+        <v>-0.0335</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.5206</v>
+        <v>-0.1825</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.9539</v>
+        <v>0.149</v>
       </c>
       <c r="P19" t="n">
-        <v>0.2175</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.305</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.5225</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>-2.4799</v>
+        <v>0.0051</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.9229000000000001</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>-1.5571</v>
+        <v>0.0051</v>
       </c>
       <c r="V19" t="n">
-        <v>1.3252</v>
+        <v>-0.1952</v>
       </c>
       <c r="W19" t="n">
-        <v>1.3252</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-0.1952</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. KELLY</t>
+          <t>A. MARTIN MARIN</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.9091</v>
+        <v>-2.9155</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.9269</v>
+        <v>-1.8213</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.9822</v>
+        <v>-1.0942</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.1091</v>
+        <v>-0.8551</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.3689</v>
+        <v>-0.0033</v>
       </c>
       <c r="I20" t="n">
-        <v>0.2598</v>
+        <v>-0.8518</v>
       </c>
       <c r="J20" t="n">
-        <v>1.0411</v>
+        <v>0.7834</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.0881</v>
+        <v>0.5324</v>
       </c>
       <c r="L20" t="n">
-        <v>1.1292</v>
+        <v>0.251</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.1502</v>
+        <v>-1.6386</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.2808</v>
+        <v>-0.5357</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.8694</v>
+        <v>-1.1029</v>
       </c>
       <c r="P20" t="n">
-        <v>-1.9576</v>
+        <v>-0.87</v>
       </c>
       <c r="Q20" t="n">
-        <v>-3.2626</v>
+        <v>-2.1751</v>
       </c>
       <c r="R20" t="n">
         <v>1.305</v>
       </c>
       <c r="S20" t="n">
-        <v>0.7226</v>
+        <v>-1.1903</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.2704</v>
+        <v>-0.6249</v>
       </c>
       <c r="U20" t="n">
-        <v>0.9929</v>
+        <v>-0.5654</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.5649999999999999</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>0.5649999999999999</v>
+        <v>0.1952</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.13</v>
+        <v>-0.1952</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>V. FAVERANI TATSCH</t>
+          <t>I. RIVERA CARROLL</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.7628</v>
+        <v>-3.3388</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.0881</v>
+        <v>-2.9016</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.6747</v>
+        <v>-0.4371</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.7488</v>
+        <v>-2.461</v>
       </c>
       <c r="H21" t="n">
-        <v>0.3255</v>
+        <v>-1.2227</v>
       </c>
       <c r="I21" t="n">
-        <v>-3.0743</v>
+        <v>-1.2383</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.3413</v>
+        <v>-2.1422</v>
       </c>
       <c r="K21" t="n">
-        <v>0.7791</v>
+        <v>-0.6903</v>
       </c>
       <c r="L21" t="n">
-        <v>-2.1204</v>
+        <v>-1.4519</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.4075</v>
+        <v>-0.3188</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.4537</v>
+        <v>-0.5324</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.9539</v>
+        <v>0.2136</v>
       </c>
       <c r="P21" t="n">
-        <v>-3.0451</v>
+        <v>-1.0875</v>
       </c>
       <c r="Q21" t="n">
-        <v>-4.5676</v>
+        <v>-1.305</v>
       </c>
       <c r="R21" t="n">
-        <v>1.5225</v>
+        <v>0.2175</v>
       </c>
       <c r="S21" t="n">
-        <v>1.4661</v>
+        <v>0.6002</v>
       </c>
       <c r="T21" t="n">
-        <v>2.1258</v>
+        <v>0.5456</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.6598000000000001</v>
+        <v>0.0547</v>
       </c>
       <c r="V21" t="n">
-        <v>0.5649999999999999</v>
+        <v>-0.3904</v>
       </c>
       <c r="W21" t="n">
-        <v>1.695</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.13</v>
+        <v>-0.3904</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A. MARTIN MARIN</t>
+          <t>A. KELLY</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.8197</v>
+        <v>-3.4805</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.2683</v>
+        <v>-1.8151</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.5514</v>
+        <v>-1.6654</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.8551</v>
+        <v>-1.1091</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.0033</v>
+        <v>-1.3689</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.8518</v>
+        <v>0.2598</v>
       </c>
       <c r="J22" t="n">
-        <v>0.7834</v>
+        <v>1.0411</v>
       </c>
       <c r="K22" t="n">
-        <v>0.5324</v>
+        <v>-0.0881</v>
       </c>
       <c r="L22" t="n">
-        <v>0.251</v>
+        <v>1.1292</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.6386</v>
+        <v>-2.1502</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.5357</v>
+        <v>-1.2808</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.1029</v>
+        <v>-0.8694</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.87</v>
+        <v>-1.9576</v>
       </c>
       <c r="Q22" t="n">
-        <v>-2.1751</v>
+        <v>-3.2626</v>
       </c>
       <c r="R22" t="n">
         <v>1.305</v>
       </c>
       <c r="S22" t="n">
-        <v>-2.0946</v>
+        <v>0.1511</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.0719</v>
+        <v>-0.1586</v>
       </c>
       <c r="U22" t="n">
-        <v>-1.0227</v>
+        <v>0.3097</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>-0.5649999999999999</v>
       </c>
       <c r="W22" t="n">
-        <v>0.1952</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.1952</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>I. RIVERA CARROLL</t>
+          <t>A. GARUBA ALARI</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.1942</v>
+        <v>-4.3455</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.5722</v>
+        <v>-2.8454</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.6221</v>
+        <v>-1.5001</v>
       </c>
       <c r="G23" t="n">
-        <v>-2.461</v>
+        <v>-3.4098</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.2227</v>
+        <v>-2.0408</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.2383</v>
+        <v>-1.369</v>
       </c>
       <c r="J23" t="n">
-        <v>-2.1422</v>
+        <v>-1.8119</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.6903</v>
+        <v>-1.1434</v>
       </c>
       <c r="L23" t="n">
-        <v>-1.4519</v>
+        <v>-0.6686</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.3188</v>
+        <v>-1.5978</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.5324</v>
+        <v>-0.8974</v>
       </c>
       <c r="O23" t="n">
-        <v>0.2136</v>
+        <v>-0.7004</v>
       </c>
       <c r="P23" t="n">
+        <v>-0.435</v>
+      </c>
+      <c r="Q23" t="n">
         <v>-1.0875</v>
       </c>
-      <c r="Q23" t="n">
-        <v>-1.305</v>
-      </c>
       <c r="R23" t="n">
-        <v>0.2175</v>
+        <v>0.6525</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.2552</v>
+        <v>0.0643</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.125</v>
+        <v>0.0541</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.1303</v>
+        <v>0.0102</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.3904</v>
+        <v>-0.5649999999999999</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.3904</v>
+        <v>-0.5649999999999999</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A. GARUBA ALARI</t>
+          <t>V. FAVERANI TATSCH</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.4559</v>
+        <v>-5.5984</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.6219</v>
+        <v>-3.7645</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.834</v>
+        <v>-1.8339</v>
       </c>
       <c r="G24" t="n">
-        <v>-3.4098</v>
+        <v>-2.7488</v>
       </c>
       <c r="H24" t="n">
-        <v>-2.0408</v>
+        <v>0.3255</v>
       </c>
       <c r="I24" t="n">
-        <v>-1.369</v>
+        <v>-3.0743</v>
       </c>
       <c r="J24" t="n">
-        <v>-1.8119</v>
+        <v>-1.3413</v>
       </c>
       <c r="K24" t="n">
-        <v>-1.1434</v>
+        <v>0.7791</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.6686</v>
+        <v>-2.1204</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.5978</v>
+        <v>-1.4075</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.8974</v>
+        <v>-0.4537</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.7004</v>
+        <v>-0.9539</v>
       </c>
       <c r="P24" t="n">
-        <v>-0.435</v>
+        <v>-3.0451</v>
       </c>
       <c r="Q24" t="n">
-        <v>-1.0875</v>
+        <v>-4.5676</v>
       </c>
       <c r="R24" t="n">
-        <v>0.6525</v>
+        <v>1.5225</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.0461</v>
+        <v>-0.3695</v>
       </c>
       <c r="T24" t="n">
-        <v>0.2776</v>
+        <v>0.4495</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.3237</v>
+        <v>-0.819</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.5649999999999999</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.695</v>
       </c>
       <c r="X24" t="n">
-        <v>-0.5649999999999999</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="25">
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-7.2138</v>
+        <v>-7.4644</v>
       </c>
       <c r="E25" t="n">
-        <v>-4.6715</v>
+        <v>-5.2303</v>
       </c>
       <c r="F25" t="n">
-        <v>-2.5423</v>
+        <v>-2.2341</v>
       </c>
       <c r="G25" t="n">
         <v>-5.7295</v>
@@ -2404,13 +2404,13 @@
         <v>0.435</v>
       </c>
       <c r="S25" t="n">
-        <v>0.9061</v>
+        <v>0.6555</v>
       </c>
       <c r="T25" t="n">
-        <v>1.4456</v>
+        <v>0.8869</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.5396</v>
+        <v>-0.2313</v>
       </c>
       <c r="V25" t="n">
         <v>-1.5204</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-26.1256</v>
+        <v>-25.3809</v>
       </c>
       <c r="E26" t="n">
         <v>-12.7532</v>
       </c>
       <c r="F26" t="n">
-        <v>-13.3725</v>
+        <v>-12.6276</v>
       </c>
       <c r="G26" t="n">
         <v>-15.1848</v>
@@ -2458,7 +2458,7 @@
         <v>-2.4053</v>
       </c>
       <c r="K26" t="n">
-        <v>0.2759000000000005</v>
+        <v>0.2759</v>
       </c>
       <c r="L26" t="n">
         <v>-2.6814</v>
@@ -2470,10 +2470,10 @@
         <v>-6.420500000000001</v>
       </c>
       <c r="O26" t="n">
-        <v>-6.359100000000001</v>
+        <v>-6.3591</v>
       </c>
       <c r="P26" t="n">
-        <v>-9.787700000000001</v>
+        <v>-9.787699999999999</v>
       </c>
       <c r="Q26" t="n">
         <v>-18.4878</v>
@@ -2482,13 +2482,13 @@
         <v>8.700000000000001</v>
       </c>
       <c r="S26" t="n">
-        <v>-1.8926</v>
+        <v>-1.1477</v>
       </c>
       <c r="T26" t="n">
-        <v>1.1236</v>
+        <v>1.1238</v>
       </c>
       <c r="U26" t="n">
-        <v>-3.0166</v>
+        <v>-2.2713</v>
       </c>
       <c r="V26" t="n">
         <v>0.7395999999999998</v>
